--- a/Decks/Toph.xlsx
+++ b/Decks/Toph.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marcelo Scalvi\Dropbox\Jogos\Magic\Decks\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marcelo Scalvi\Dropbox\Jogos\TheMagicCollection\Decks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB965255-8AF7-4552-A35F-54AB94625D2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DF031BB-9738-4D32-8AC5-5A708DBA4E83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{94366DDF-8398-4638-94DC-61569ED5A585}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="122">
   <si>
     <t>Função</t>
   </si>
@@ -192,9 +192,6 @@
   </si>
   <si>
     <t>Arcane Spyglass</t>
-  </si>
-  <si>
-    <t>Evendo Brushrazer</t>
   </si>
   <si>
     <t>Aranã, Heart of the Spider</t>
@@ -983,10 +980,10 @@
         <v>0</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -1013,10 +1010,10 @@
         <v>0</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -1028,10 +1025,10 @@
         <v>0</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -1556,7 +1553,7 @@
         <v>51</v>
       </c>
       <c r="D49" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.25">
@@ -1565,13 +1562,13 @@
       </c>
       <c r="B50" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>52</v>
+        <v>112</v>
       </c>
       <c r="D50" s="6" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.25">
@@ -1583,10 +1580,10 @@
         <v>0</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D51" s="6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.25">
@@ -1598,10 +1595,10 @@
         <v>1</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D52" s="6" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.25">
@@ -1613,10 +1610,10 @@
         <v>0</v>
       </c>
       <c r="C53" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D53" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.25">
@@ -1628,10 +1625,10 @@
         <v>1</v>
       </c>
       <c r="C54" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="D54" s="6" t="s">
         <v>55</v>
-      </c>
-      <c r="D54" s="6" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.25">
@@ -1643,10 +1640,10 @@
         <v>1</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D55" s="6" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.25">
@@ -1658,10 +1655,10 @@
         <v>0</v>
       </c>
       <c r="C56" s="6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D56" s="6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.25">
@@ -1673,698 +1670,698 @@
         <v>0</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D57" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
+        <v>59</v>
+      </c>
+      <c r="B58" s="5" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C58" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="B58" s="5" t="b">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="C58" s="6" t="s">
-        <v>61</v>
-      </c>
       <c r="D58" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B59" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C59" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D59" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="L59" s="6"/>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B60" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C60" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D60" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="L60" s="6"/>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B61" s="5" t="b">
         <f>C61&lt;&gt;D61</f>
         <v>0</v>
       </c>
       <c r="C61" s="6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D61" s="6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="L61" s="6"/>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B62" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C62" s="6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D62" s="6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="L62" s="6"/>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B63" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C63" s="6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D63" s="6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="L63" s="6"/>
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B64" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C64" s="6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D64" s="6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="L64" s="6"/>
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B65" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C65" s="6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D65" s="6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="L65" s="6"/>
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B66" s="5" t="b">
         <f t="shared" ref="B66:B101" si="1">C66&lt;&gt;D66</f>
         <v>0</v>
       </c>
       <c r="C66" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D66" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B67" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C67" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D67" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B68" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C68" s="6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D68" s="6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B69" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C69" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D69" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B70" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C70" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D70" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B71" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C71" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D71" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B72" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C72" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D72" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B73" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C73" s="6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D73" s="6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B74" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C74" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D74" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B75" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C75" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D75" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B76" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C76" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D76" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B77" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C77" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D77" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
+        <v>81</v>
+      </c>
+      <c r="B78" s="5" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C78" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="B78" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="C78" s="6" t="s">
-        <v>83</v>
-      </c>
       <c r="D78" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B79" s="5" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="C79" s="6" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D79" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="L79" s="6"/>
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
+        <v>84</v>
+      </c>
+      <c r="B80" s="5" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C80" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="B80" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="C80" s="6" t="s">
-        <v>86</v>
-      </c>
       <c r="D80" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="L80" s="6"/>
     </row>
     <row r="81" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B81" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C81" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D81" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="K81" s="6"/>
       <c r="L81" s="6"/>
     </row>
     <row r="82" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B82" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C82" s="6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D82" s="6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="L82" s="6"/>
     </row>
     <row r="83" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B83" s="5" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="C83" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D83" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="L83" s="6"/>
     </row>
     <row r="84" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B84" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C84" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D84" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="L84" s="6"/>
     </row>
     <row r="85" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B85" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C85" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D85" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="L85" s="6"/>
     </row>
     <row r="86" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B86" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C86" s="6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D86" s="6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="L86" s="6"/>
     </row>
     <row r="87" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B87" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C87" s="6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D87" s="6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="L87" s="6"/>
     </row>
     <row r="88" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B88" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C88" s="6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D88" s="6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="L88" s="6"/>
     </row>
     <row r="89" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B89" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C89" s="6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D89" s="6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L89" s="6"/>
     </row>
     <row r="90" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B90" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C90" s="6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D90" s="6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="L90" s="6"/>
     </row>
     <row r="91" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B91" s="5" t="b">
         <f>C91&lt;&gt;D91</f>
         <v>1</v>
       </c>
       <c r="C91" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="D91" s="6" t="s">
         <v>110</v>
-      </c>
-      <c r="D91" s="6" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="92" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B92" s="5" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="C92" s="6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D92" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="L92" s="6"/>
     </row>
     <row r="93" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
+        <v>96</v>
+      </c>
+      <c r="B93" s="5" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C93" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="B93" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="C93" s="6" t="s">
-        <v>98</v>
-      </c>
       <c r="D93" s="6" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="L93" s="6"/>
     </row>
     <row r="94" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B94" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C94" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D94" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="L94" s="6"/>
     </row>
     <row r="95" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B95" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C95" s="6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D95" s="6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="L95" s="6"/>
     </row>
     <row r="96" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B96" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C96" s="6" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D96" s="6" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="L96" s="6"/>
     </row>
     <row r="97" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B97" s="5" t="b">
         <f>C97&lt;&gt;D97</f>
         <v>0</v>
       </c>
       <c r="C97" s="6" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D97" s="6" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="98" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
+        <v>101</v>
+      </c>
+      <c r="B98" s="5" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C98" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="B98" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="C98" s="6" t="s">
-        <v>103</v>
-      </c>
       <c r="D98" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="L98" s="6"/>
     </row>
     <row r="99" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B99" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C99" s="6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D99" s="6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="L99" s="6"/>
     </row>
     <row r="100" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B100" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C100" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D100" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="L100" s="6"/>
     </row>
     <row r="101" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B101" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C101" s="6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D101" s="6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
   </sheetData>

--- a/Decks/Toph.xlsx
+++ b/Decks/Toph.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marcelo Scalvi\Dropbox\Jogos\TheMagicCollection\Decks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DF031BB-9738-4D32-8AC5-5A708DBA4E83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{725B81BC-D377-4F1D-85E9-6A132895933F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{94366DDF-8398-4638-94DC-61569ED5A585}"/>
   </bookViews>
@@ -194,9 +194,6 @@
     <t>Arcane Spyglass</t>
   </si>
   <si>
-    <t>Aranã, Heart of the Spider</t>
-  </si>
-  <si>
     <t>Long-Range Sensor</t>
   </si>
   <si>
@@ -402,6 +399,9 @@
   </si>
   <si>
     <t>Urborg, Tomb of Yawgmoth</t>
+  </si>
+  <si>
+    <t>Ark of Hunger</t>
   </si>
 </sst>
 </file>
@@ -980,10 +980,10 @@
         <v>0</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -1010,10 +1010,10 @@
         <v>0</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -1025,10 +1025,10 @@
         <v>0</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -1553,7 +1553,7 @@
         <v>51</v>
       </c>
       <c r="D49" s="6" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.25">
@@ -1565,10 +1565,10 @@
         <v>0</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D50" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.25">
@@ -1580,10 +1580,10 @@
         <v>0</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D51" s="6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.25">
@@ -1595,10 +1595,10 @@
         <v>1</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>52</v>
+        <v>121</v>
       </c>
       <c r="D52" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.25">
@@ -1610,10 +1610,10 @@
         <v>0</v>
       </c>
       <c r="C53" s="6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D53" s="6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.25">
@@ -1625,10 +1625,10 @@
         <v>1</v>
       </c>
       <c r="C54" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="D54" s="6" t="s">
         <v>54</v>
-      </c>
-      <c r="D54" s="6" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.25">
@@ -1640,10 +1640,10 @@
         <v>1</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D55" s="6" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.25">
@@ -1655,10 +1655,10 @@
         <v>0</v>
       </c>
       <c r="C56" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D56" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.25">
@@ -1670,698 +1670,698 @@
         <v>0</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D57" s="6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
+        <v>58</v>
+      </c>
+      <c r="B58" s="5" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C58" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="B58" s="5" t="b">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="C58" s="6" t="s">
-        <v>60</v>
-      </c>
       <c r="D58" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B59" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C59" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D59" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="L59" s="6"/>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B60" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C60" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D60" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="L60" s="6"/>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B61" s="5" t="b">
         <f>C61&lt;&gt;D61</f>
         <v>0</v>
       </c>
       <c r="C61" s="6" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D61" s="6" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="L61" s="6"/>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B62" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C62" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D62" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="L62" s="6"/>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B63" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C63" s="6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D63" s="6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="L63" s="6"/>
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B64" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C64" s="6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D64" s="6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="L64" s="6"/>
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B65" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C65" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D65" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="L65" s="6"/>
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B66" s="5" t="b">
         <f t="shared" ref="B66:B101" si="1">C66&lt;&gt;D66</f>
         <v>0</v>
       </c>
       <c r="C66" s="6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D66" s="6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B67" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C67" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D67" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B68" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C68" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D68" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B69" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C69" s="6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D69" s="6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B70" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C70" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D70" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B71" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C71" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D71" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B72" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C72" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D72" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B73" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C73" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D73" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B74" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C74" s="6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D74" s="6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B75" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C75" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D75" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B76" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C76" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D76" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B77" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C77" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D77" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
+        <v>80</v>
+      </c>
+      <c r="B78" s="5" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C78" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="B78" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="C78" s="6" t="s">
-        <v>82</v>
-      </c>
       <c r="D78" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B79" s="5" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="C79" s="6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D79" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="L79" s="6"/>
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
+        <v>83</v>
+      </c>
+      <c r="B80" s="5" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C80" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="B80" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="C80" s="6" t="s">
-        <v>85</v>
-      </c>
       <c r="D80" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="L80" s="6"/>
     </row>
     <row r="81" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B81" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C81" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D81" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="K81" s="6"/>
       <c r="L81" s="6"/>
     </row>
     <row r="82" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B82" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C82" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D82" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="L82" s="6"/>
     </row>
     <row r="83" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B83" s="5" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="C83" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D83" s="6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="L83" s="6"/>
     </row>
     <row r="84" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B84" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C84" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D84" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="L84" s="6"/>
     </row>
     <row r="85" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B85" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C85" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D85" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="L85" s="6"/>
     </row>
     <row r="86" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B86" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C86" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D86" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="L86" s="6"/>
     </row>
     <row r="87" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B87" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C87" s="6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D87" s="6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="L87" s="6"/>
     </row>
     <row r="88" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B88" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C88" s="6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D88" s="6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="L88" s="6"/>
     </row>
     <row r="89" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B89" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C89" s="6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D89" s="6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="L89" s="6"/>
     </row>
     <row r="90" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B90" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C90" s="6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D90" s="6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L90" s="6"/>
     </row>
     <row r="91" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B91" s="5" t="b">
         <f>C91&lt;&gt;D91</f>
         <v>1</v>
       </c>
       <c r="C91" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="D91" s="6" t="s">
         <v>109</v>
-      </c>
-      <c r="D91" s="6" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="92" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B92" s="5" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="C92" s="6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D92" s="6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="L92" s="6"/>
     </row>
     <row r="93" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
+        <v>95</v>
+      </c>
+      <c r="B93" s="5" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C93" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="B93" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="C93" s="6" t="s">
-        <v>97</v>
-      </c>
       <c r="D93" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="L93" s="6"/>
     </row>
     <row r="94" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B94" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C94" s="6" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D94" s="6" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="L94" s="6"/>
     </row>
     <row r="95" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B95" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C95" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D95" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="L95" s="6"/>
     </row>
     <row r="96" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B96" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C96" s="6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D96" s="6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="L96" s="6"/>
     </row>
     <row r="97" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B97" s="5" t="b">
         <f>C97&lt;&gt;D97</f>
         <v>0</v>
       </c>
       <c r="C97" s="6" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D97" s="6" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="98" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
+        <v>100</v>
+      </c>
+      <c r="B98" s="5" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C98" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="B98" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="C98" s="6" t="s">
-        <v>102</v>
-      </c>
       <c r="D98" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L98" s="6"/>
     </row>
     <row r="99" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B99" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C99" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D99" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="L99" s="6"/>
     </row>
     <row r="100" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B100" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C100" s="6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D100" s="6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="L100" s="6"/>
     </row>
     <row r="101" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B101" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C101" s="6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D101" s="6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
   </sheetData>

--- a/Decks/Toph.xlsx
+++ b/Decks/Toph.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marcelo Scalvi\Dropbox\Jogos\TheMagicCollection\Decks\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Dropbox\Jogos\TheMagicCollection\Decks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{725B81BC-D377-4F1D-85E9-6A132895933F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A194318D-5183-4F75-A718-CB9254A02CCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{94366DDF-8398-4638-94DC-61569ED5A585}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{94366DDF-8398-4638-94DC-61569ED5A585}"/>
   </bookViews>
   <sheets>
     <sheet name="Modular" sheetId="1" r:id="rId1"/>
@@ -356,9 +356,6 @@
     <t>Kirol, Attentive First-Year</t>
   </si>
   <si>
-    <t>Arcobund Slith</t>
-  </si>
-  <si>
     <t>Dyadrine, Synthesis Amalgam</t>
   </si>
   <si>
@@ -402,6 +399,9 @@
   </si>
   <si>
     <t>Ark of Hunger</t>
+  </si>
+  <si>
+    <t>Arcbound Slith</t>
   </si>
 </sst>
 </file>
@@ -980,10 +980,10 @@
         <v>0</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -1010,10 +1010,10 @@
         <v>0</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -1025,10 +1025,10 @@
         <v>0</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -1553,7 +1553,7 @@
         <v>51</v>
       </c>
       <c r="D49" s="6" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.25">
@@ -1565,10 +1565,10 @@
         <v>0</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D50" s="6" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.25">
@@ -1580,10 +1580,10 @@
         <v>0</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D51" s="6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.25">
@@ -1595,10 +1595,10 @@
         <v>1</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D52" s="6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.25">
@@ -1643,7 +1643,7 @@
         <v>55</v>
       </c>
       <c r="D55" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.25">
@@ -1732,10 +1732,10 @@
         <v>0</v>
       </c>
       <c r="C61" s="6" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D61" s="6" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="L61" s="6"/>
     </row>
@@ -2007,7 +2007,7 @@
         <v>1</v>
       </c>
       <c r="C79" s="6" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D79" s="6" t="s">
         <v>82</v>
@@ -2200,10 +2200,10 @@
         <v>1</v>
       </c>
       <c r="C91" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="D91" s="6" t="s">
         <v>108</v>
-      </c>
-      <c r="D91" s="6" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="92" spans="1:12" x14ac:dyDescent="0.25">
@@ -2215,10 +2215,10 @@
         <v>1</v>
       </c>
       <c r="C92" s="6" t="s">
-        <v>106</v>
+        <v>121</v>
       </c>
       <c r="D92" s="6" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="L92" s="6"/>
     </row>
@@ -2295,10 +2295,10 @@
         <v>0</v>
       </c>
       <c r="C97" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D97" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="98" spans="1:12" x14ac:dyDescent="0.25">

--- a/Decks/Toph.xlsx
+++ b/Decks/Toph.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Dropbox\Jogos\TheMagicCollection\Decks\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marcelo Scalvi\Dropbox\Jogos\TheMagicCollection\Decks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A194318D-5183-4F75-A718-CB9254A02CCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{531BBABB-BE31-4257-A862-F43799ADBB3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{94366DDF-8398-4638-94DC-61569ED5A585}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{94366DDF-8398-4638-94DC-61569ED5A585}"/>
   </bookViews>
   <sheets>
     <sheet name="Modular" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="121">
   <si>
     <t>Função</t>
   </si>
@@ -152,9 +152,6 @@
     <t>Ramp</t>
   </si>
   <si>
-    <t>Harrow</t>
-  </si>
-  <si>
     <t>Sol Ring</t>
   </si>
   <si>
@@ -176,9 +173,6 @@
     <t>Earthbender Ascension</t>
   </si>
   <si>
-    <t>The Earth King</t>
-  </si>
-  <si>
     <t>Draw</t>
   </si>
   <si>
@@ -191,9 +185,6 @@
     <t>Marketback Walker</t>
   </si>
   <si>
-    <t>Arcane Spyglass</t>
-  </si>
-  <si>
     <t>Long-Range Sensor</t>
   </si>
   <si>
@@ -203,9 +194,6 @@
     <t>The Great Henge</t>
   </si>
   <si>
-    <t>Mindless Automaton</t>
-  </si>
-  <si>
     <t>Tannuk, Memorial Ensign</t>
   </si>
   <si>
@@ -296,9 +284,6 @@
     <t>Throne of Geth</t>
   </si>
   <si>
-    <t>Costume Closet</t>
-  </si>
-  <si>
     <t>Filigree Vector</t>
   </si>
   <si>
@@ -402,6 +387,18 @@
   </si>
   <si>
     <t>Arcbound Slith</t>
+  </si>
+  <si>
+    <t>Blossoming Tortoise</t>
+  </si>
+  <si>
+    <t>Sunken Citadel</t>
+  </si>
+  <si>
+    <t>Hourglass of the Lost</t>
+  </si>
+  <si>
+    <t>Coin of Mastery</t>
   </si>
 </sst>
 </file>
@@ -856,7 +853,7 @@
         <v>8</v>
       </c>
       <c r="B3" s="5" t="b">
-        <f t="shared" ref="B3:B65" si="0">C3&lt;&gt;D3</f>
+        <f t="shared" ref="B3:B67" si="0">C3&lt;&gt;D3</f>
         <v>0</v>
       </c>
       <c r="C3" s="6" t="s">
@@ -980,10 +977,10 @@
         <v>0</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -1010,10 +1007,10 @@
         <v>0</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -1025,10 +1022,10 @@
         <v>0</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -1250,10 +1247,10 @@
         <v>0</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>36</v>
+        <v>118</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>36</v>
+        <v>118</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -1301,7 +1298,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>8</v>
       </c>
@@ -1316,7 +1313,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>8</v>
       </c>
@@ -1331,7 +1328,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>8</v>
       </c>
@@ -1346,7 +1343,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>8</v>
       </c>
@@ -1361,7 +1358,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>8</v>
       </c>
@@ -1376,7 +1373,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>37</v>
       </c>
@@ -1385,13 +1382,13 @@
         <v>0</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>37</v>
       </c>
@@ -1400,13 +1397,13 @@
         <v>0</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>37</v>
       </c>
@@ -1415,13 +1412,13 @@
         <v>0</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>37</v>
       </c>
@@ -1430,13 +1427,13 @@
         <v>0</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>37</v>
       </c>
@@ -1445,28 +1442,28 @@
         <v>0</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>37</v>
       </c>
       <c r="B43" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>37</v>
       </c>
@@ -1475,13 +1472,13 @@
         <v>0</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>37</v>
       </c>
@@ -1490,878 +1487,881 @@
         <v>0</v>
       </c>
       <c r="C45" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="D45" s="6" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>37</v>
+      </c>
+      <c r="B46" s="5" t="b">
+        <f>C46&lt;&gt;D46</f>
+        <v>1</v>
+      </c>
+      <c r="C46" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="D46" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="L46" s="6"/>
+    </row>
+    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>37</v>
+      </c>
+      <c r="B47" s="5" t="b">
+        <f>C47&lt;&gt;D47</f>
+        <v>0</v>
+      </c>
+      <c r="C47" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="D47" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>45</v>
+      </c>
+      <c r="B48" s="5" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C48" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="D45" s="6" t="s">
+      <c r="D48" s="6" t="s">
         <v>46</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>47</v>
-      </c>
-      <c r="B46" s="5" t="b">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="C46" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="D46" s="6" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>47</v>
-      </c>
-      <c r="B47" s="5" t="b">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="C47" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="D47" s="6" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>47</v>
-      </c>
-      <c r="B48" s="5" t="b">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="C48" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="D48" s="6" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
+        <v>45</v>
+      </c>
+      <c r="B49" s="5" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C49" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="B49" s="5" t="b">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="C49" s="6" t="s">
-        <v>51</v>
-      </c>
       <c r="D49" s="6" t="s">
-        <v>109</v>
+        <v>47</v>
       </c>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B50" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>110</v>
+        <v>48</v>
       </c>
       <c r="D50" s="6" t="s">
-        <v>110</v>
+        <v>48</v>
       </c>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B51" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="D51" s="6" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B52" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>120</v>
+        <v>105</v>
       </c>
       <c r="D52" s="6" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B53" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C53" s="6" t="s">
-        <v>52</v>
+        <v>101</v>
       </c>
       <c r="D53" s="6" t="s">
-        <v>52</v>
+        <v>101</v>
       </c>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B54" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C54" s="6" t="s">
-        <v>53</v>
+        <v>109</v>
       </c>
       <c r="D54" s="6" t="s">
-        <v>54</v>
+        <v>109</v>
       </c>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B55" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="D55" s="6" t="s">
-        <v>115</v>
+        <v>49</v>
       </c>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B56" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C56" s="6" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="D56" s="6" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B57" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>57</v>
+        <v>110</v>
       </c>
       <c r="D57" s="6" t="s">
-        <v>57</v>
+        <v>110</v>
       </c>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="B58" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C58" s="6" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="D58" s="6" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="B59" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C59" s="6" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="D59" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="L59" s="6"/>
+        <v>53</v>
+      </c>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="B60" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C60" s="6" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D60" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="L60" s="6"/>
+        <v>55</v>
+      </c>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="B61" s="5" t="b">
-        <f>C61&lt;&gt;D61</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C61" s="6" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="D61" s="6" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="L61" s="6"/>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="B62" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C62" s="6" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="D62" s="6" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="L62" s="6"/>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="B63" s="5" t="b">
-        <f t="shared" si="0"/>
+        <f>C63&lt;&gt;D63</f>
         <v>0</v>
       </c>
       <c r="C63" s="6" t="s">
-        <v>65</v>
+        <v>107</v>
       </c>
       <c r="D63" s="6" t="s">
-        <v>65</v>
+        <v>107</v>
       </c>
       <c r="L63" s="6"/>
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="B64" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C64" s="6" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="D64" s="6" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="L64" s="6"/>
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="B65" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C65" s="6" t="s">
-        <v>104</v>
+        <v>61</v>
       </c>
       <c r="D65" s="6" t="s">
-        <v>104</v>
+        <v>61</v>
       </c>
       <c r="L65" s="6"/>
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="B66" s="5" t="b">
-        <f t="shared" ref="B66:B101" si="1">C66&lt;&gt;D66</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C66" s="6" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="D66" s="6" t="s">
-        <v>68</v>
-      </c>
+        <v>62</v>
+      </c>
+      <c r="L66" s="6"/>
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="B67" s="5" t="b">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C67" s="6" t="s">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="D67" s="6" t="s">
-        <v>69</v>
-      </c>
+        <v>99</v>
+      </c>
+      <c r="L67" s="6"/>
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B68" s="5" t="b">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="B68:B101" si="1">C68&lt;&gt;D68</f>
         <v>0</v>
       </c>
       <c r="C68" s="6" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="D68" s="6" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B69" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C69" s="6" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="D69" s="6" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B70" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C70" s="6" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="D70" s="6" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
+        <v>63</v>
+      </c>
+      <c r="B71" s="5" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C71" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="B71" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="C71" s="6" t="s">
-        <v>73</v>
-      </c>
       <c r="D71" s="6" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B72" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C72" s="6" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="D72" s="6" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B73" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C73" s="6" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="D73" s="6" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B74" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C74" s="6" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="D74" s="6" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B75" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C75" s="6" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="D75" s="6" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B76" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C76" s="6" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="D76" s="6" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B77" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C77" s="6" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="D77" s="6" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>80</v>
+        <v>63</v>
       </c>
       <c r="B78" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C78" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="D78" t="s">
-        <v>81</v>
+        <v>74</v>
+      </c>
+      <c r="D78" s="6" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>80</v>
+        <v>63</v>
       </c>
       <c r="B79" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C79" s="6" t="s">
-        <v>117</v>
+        <v>75</v>
       </c>
       <c r="D79" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="L79" s="6"/>
+        <v>75</v>
+      </c>
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="B80" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C80" s="6" t="s">
-        <v>84</v>
+        <v>112</v>
       </c>
       <c r="D80" s="6" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="L80" s="6"/>
     </row>
     <row r="81" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="B81" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C81" s="6" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="D81" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="K81" s="6"/>
+        <v>80</v>
+      </c>
       <c r="L81" s="6"/>
     </row>
     <row r="82" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="B82" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C82" s="6" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="D82" s="6" t="s">
-        <v>86</v>
-      </c>
+        <v>81</v>
+      </c>
+      <c r="K82" s="6"/>
       <c r="L82" s="6"/>
     </row>
     <row r="83" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="B83" s="5" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="C83" s="6" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="D83" s="6" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="L83" s="6"/>
     </row>
     <row r="84" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
+        <v>79</v>
+      </c>
+      <c r="B84" s="5" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C84" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="B84" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="C84" s="6" t="s">
-        <v>88</v>
-      </c>
       <c r="D84" s="6" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="L84" s="6"/>
     </row>
     <row r="85" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="B85" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C85" s="6" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="D85" s="6" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="L85" s="6"/>
     </row>
     <row r="86" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="B86" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C86" s="6" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="D86" s="6" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="L86" s="6"/>
     </row>
     <row r="87" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="B87" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C87" s="6" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="D87" s="6" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="L87" s="6"/>
     </row>
     <row r="88" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="B88" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C88" s="6" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="D88" s="6" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="L88" s="6"/>
     </row>
     <row r="89" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="B89" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C89" s="6" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="D89" s="6" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="L89" s="6"/>
     </row>
     <row r="90" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="B90" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C90" s="6" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="D90" s="6" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="L90" s="6"/>
     </row>
     <row r="91" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="B91" s="5" t="b">
         <f>C91&lt;&gt;D91</f>
         <v>1</v>
       </c>
       <c r="C91" s="6" t="s">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="D91" s="6" t="s">
-        <v>108</v>
+        <v>117</v>
+      </c>
+      <c r="E91" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="92" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="B92" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C92" s="6" t="s">
-        <v>121</v>
+        <v>108</v>
       </c>
       <c r="D92" s="6" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="L92" s="6"/>
     </row>
     <row r="93" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="B93" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C93" s="6" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="D93" s="6" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="L93" s="6"/>
     </row>
     <row r="94" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="B94" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C94" s="6" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="D94" s="6" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="L94" s="6"/>
     </row>
     <row r="95" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="B95" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C95" s="6" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="D95" s="6" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="L95" s="6"/>
     </row>
     <row r="96" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="B96" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C96" s="6" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="D96" s="6" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="L96" s="6"/>
     </row>
     <row r="97" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="B97" s="5" t="b">
         <f>C97&lt;&gt;D97</f>
         <v>0</v>
       </c>
       <c r="C97" s="6" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="D97" s="6" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
     </row>
     <row r="98" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="B98" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C98" s="6" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="D98" s="6" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="L98" s="6"/>
     </row>
     <row r="99" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="B99" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C99" s="6" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="D99" s="6" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="L99" s="6"/>
     </row>
     <row r="100" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="B100" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C100" s="6" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="D100" s="6" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="L100" s="6"/>
     </row>
     <row r="101" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
+        <v>95</v>
+      </c>
+      <c r="B101" s="5" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C101" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="B101" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="C101" s="6" t="s">
-        <v>105</v>
-      </c>
       <c r="D101" s="6" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>
